--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>73880555</v>
       </c>
       <c r="B2" t="n">
-        <v>90224</v>
+        <v>90234</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,12 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -948,10 +943,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515943.9275245179</v>
+        <v>515944</v>
       </c>
       <c r="R4" t="n">
-        <v>6362637.680638303</v>
+        <v>6362638</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -981,19 +976,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1037,12 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>105642</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1074,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515943.9275245179</v>
+        <v>515944</v>
       </c>
       <c r="R5" t="n">
-        <v>6362637.680638303</v>
+        <v>6362638</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1107,19 +1087,9 @@
           <t>1989-01-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1991-12-31</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98588</v>
+        <v>98591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105642</v>
+        <v>105651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98591</v>
+        <v>98592</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105651</v>
+        <v>105654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98592</v>
+        <v>98619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105654</v>
+        <v>105682</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98619</v>
+        <v>98625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105682</v>
+        <v>105688</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98625</v>
+        <v>98632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105688</v>
+        <v>105695</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105695</v>
+        <v>105699</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105699</v>
+        <v>105706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98646</v>
+        <v>98651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105709</v>
+        <v>105714</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105714</v>
+        <v>105722</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -911,7 +911,7 @@
         <v>74469541</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         <v>74857099</v>
       </c>
       <c r="B5" t="n">
-        <v>105722</v>
+        <v>105732</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -764,7 +764,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">

--- a/artfynd/A 47577-2023 artfynd.xlsx
+++ b/artfynd/A 47577-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
           <t>Kalkbarrsvampar 2018</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73880555</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
           <t>Kalkbarrsvampar 2018</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73880587</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -996,6 +1011,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74469541</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1107,8 +1127,19 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74857099</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>